--- a/contenus/tab2/exs8-tcd-comptage-categorie.xlsx
+++ b/contenus/tab2/exs8-tcd-comptage-categorie.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consignes" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercice" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Correction" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1035,376 +1034,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Référence</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Catégorie</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>REF801</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>EPI</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>REF802</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>EPI</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>REF803</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>EPI</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>REF804</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>EPI</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>REF805</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>EPI</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>REF806</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Emballage</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>REF807</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Emballage</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>REF808</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Emballage</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>REF809</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Emballage</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>REF810</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Emballage</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>REF811</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Emballage</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>REF812</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Emballage</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>REF813</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Matériel</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>REF814</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Matériel</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>REF815</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Matériel</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>REF816</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Matériel</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>REF817</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>REF818</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>REF819</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>REF820</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>REF821</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>REF822</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>REF823</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>REF824</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Catégorie</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Nombre</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>EPI</t>
-        </is>
-      </c>
-      <c r="B29">
-        <f>COUNTIF(B2:B25,A29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Emballage</t>
-        </is>
-      </c>
-      <c r="B30">
-        <f>COUNTIF(B2:B25,A30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Matériel</t>
-        </is>
-      </c>
-      <c r="B31">
-        <f>COUNTIF(B2:B25,A31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-      <c r="B32">
-        <f>COUNTIF(B2:B25,A32)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>